--- a/SD_year1_awardees.xlsx
+++ b/SD_year1_awardees.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t xml:space="preserve">field</t>
   </si>
@@ -43,19 +43,19 @@
     <t xml:space="preserve">Hospital dollars confirmed</t>
   </si>
   <si>
-    <t xml:space="preserve">$0. No recipient is named, so no dollar can be traced to a hospital.</t>
+    <t xml:space="preserve">$0 from these releases: they name nobody. The Rural Strong contracts later named on OpenSD include hospital rows, and those dollars are counted in sd_rht_contracts.csv ONLY -- never here.</t>
   </si>
   <si>
     <t xml:space="preserve">Where the names would be</t>
   </si>
   <si>
-    <t xml:space="preserve">ruralhealthtransformation.sd.gov (named as the resource site in both releases, refused at CONNECT), or open.sd.gov once contracts are finalised (re-probed this session: still not there).</t>
+    <t xml:space="preserve">open.sd.gov, as contracts are finalised: 8 of the 28 Rural Strong grants are there as of 2026-09-24 (R/03i); none of the 82 Technology and data grants.</t>
   </si>
   <si>
     <t xml:space="preserve">Do not add this to</t>
   </si>
   <si>
-    <t xml:space="preserve">data/reference/sd_rht_contracts.csv ($5,618,367 of ADMINISTRATIVE spend, 13 contracts). Different documents, different tiers of certainty; read both headers before combining.</t>
+    <t xml:space="preserve">data/reference/sd_rht_contracts.csv. Its ADMINISTRATIVE pool is in neither round; its RURAL STRONG pool (round_id RS) is INSIDE the $31.5M round here -- the same money named at a finer grain. Read named_elsewhere_grants / named_elsewhere_amount, and both headers, before combining anything.</t>
   </si>
   <si>
     <t xml:space="preserve">Rebuild</t>
@@ -181,6 +181,15 @@
     <t xml:space="preserve">kb_permalink</t>
   </si>
   <si>
+    <t xml:space="preserve">named_elsewhere_grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">named_elsewhere_amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">named_elsewhere_file</t>
+  </si>
+  <si>
     <t xml:space="preserve">SD</t>
   </si>
   <si>
@@ -193,7 +202,7 @@
     <t xml:space="preserve">Unclear</t>
   </si>
   <si>
-    <t xml:space="preserve">Governor Rhoden announced 28 'Rural Strong' grants totalling $31.5M supporting projects 'across 20 health systems'. THE RELEASE NAMES NO RECIPIENT. It also states the contracts will be published on OpenSD 'once finalized'; five weeks later they are not there (R/03i --probe: the RHT series is 13 administrative contracts, 'Rural Strong' returns zero rows).</t>
+    <t xml:space="preserve">Governor Rhoden announced 28 'Rural Strong' grants totalling $31.5M supporting projects 'across 20 health systems'. THE RELEASE NAMES NO RECIPIENT. It also states the contracts will be published on OpenSD 'once finalized'. As of 2026-09-24 some are: see named_elsewhere_grants -- those contracts are in sd_rht_contracts.csv (round_id RS), INSIDE this row's round_amount and never to be added to it.</t>
   </si>
   <si>
     <t xml:space="preserve">No</t>
@@ -229,7 +238,7 @@
     <t xml:space="preserve">PASS_THROUGH_UNRESOLVED</t>
   </si>
   <si>
-    <t xml:space="preserve">South Dakota announced this round but has published no recipient-level list. recipient_confirmed = No and flag_reason = RECIPIENT_NAMES_NOT_CAPTURED: the count and the round total are confirmed from the state's own release, the names are not captured, and NOTHING IS IMPUTED (spec 0.3, 0.4). distributed_to_hospital = Unclear because the release describes a mixed recipient set and never states that a hospital received money; coding Yes off 'health systems' would be the eligibility-is-not-receipt error. `amount` is deliberately empty -- the published figure is a ROUND total, not one recipient's award, and it lives in `round_amount` so no sum over `amount` can read as a per-recipient total (6.2, the Georgia rule). This row is NOT part of South Dakota's 13 administrative RHT contracts ($5,618,367, data/reference/sd_rht_contracts.csv); the two must never be added together without reading both files' headers.</t>
+    <t xml:space="preserve">South Dakota announced this round but has published no recipient-level list. recipient_confirmed = No and flag_reason = RECIPIENT_NAMES_NOT_CAPTURED: the count and the round total are confirmed from the state's own release, the names are not captured, and NOTHING IS IMPUTED (spec 0.3, 0.4). distributed_to_hospital = Unclear because the release describes a mixed recipient set and never states that a hospital received money; coding Yes off 'health systems' would be the eligibility-is-not-receipt error. `amount` is deliberately empty -- the published figure is a ROUND total, not one recipient's award, and it lives in `round_amount` so no sum over `amount` can read as a per-recipient total (6.2, the Georgia rule). RELATION TO data/reference/sd_rht_contracts.csv: that file's ADMINISTRATIVE pool is NOT part of either round, and its RURAL STRONG pool (round_id RS) is INSIDE the Rural Strong row's round_amount -- the same money named at a finer grain -- so no sum may add a round_amount here to any amount there without reading both files' headers.</t>
   </si>
   <si>
     <t xml:space="preserve">data/evidence/SD/announcements/KB0046839.html</t>
@@ -238,7 +247,7 @@
     <t xml:space="preserve">NOT_PUBLISHED</t>
   </si>
   <si>
-    <t xml:space="preserve">CONTRACTS_PENDING</t>
+    <t xml:space="preserve">CONTRACTS_PARTLY_POSTED</t>
   </si>
   <si>
     <t xml:space="preserve">AGGREGATE_ROUND</t>
@@ -262,6 +271,9 @@
     <t xml:space="preserve">https://news.sd.gov/kb_view.do?sysparm_article=KB0046839</t>
   </si>
   <si>
+    <t xml:space="preserve">data/reference/sd_rht_contracts.csv</t>
+  </si>
+  <si>
     <t xml:space="preserve">82 grants (Technology and data grants) to 82 rural healthcare organizations - recipient names not published</t>
   </si>
   <si>
@@ -310,22 +322,28 @@
     <t xml:space="preserve">Rural Strong project grants (2026-07-23)</t>
   </si>
   <si>
+    <t xml:space="preserve">  of which named on open.sd.gov (INSIDE the line above, never added)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  of which named nowhere (amount stated by no source; not computed)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technology and data grants (2026-08-19)</t>
   </si>
   <si>
-    <t xml:space="preserve">Announced, recipients NOT published</t>
+    <t xml:space="preserve">Announced rounds, total</t>
   </si>
   <si>
     <t xml:space="preserve">Named recipients captured from these releases</t>
   </si>
   <si>
-    <t xml:space="preserve">Administrative contracts on open.sd.gov (R/03i)</t>
+    <t xml:space="preserve">Administrative contracts on open.sd.gov (R/03i, NOT in either round)</t>
   </si>
   <si>
     <t xml:space="preserve">CMS Year 1 award to South Dakota</t>
   </si>
   <si>
-    <t xml:space="preserve">Unaccounted against the CMS award</t>
+    <t xml:space="preserve">Unaccounted against the CMS award (announced rounds + administrative only)</t>
   </si>
 </sst>
 </file>
@@ -847,100 +865,109 @@
       <c r="AM1" t="s">
         <v>54</v>
       </c>
+      <c r="AN1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D2"/>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="O2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P2"/>
       <c r="Q2"/>
       <c r="R2"/>
       <c r="S2"/>
       <c r="T2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="U2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="V2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="X2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Y2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Z2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AA2"/>
       <c r="AB2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AC2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AD2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AE2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AF2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AG2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AI2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AJ2" t="n">
         <v>28</v>
@@ -949,105 +976,114 @@
         <v>31500000</v>
       </c>
       <c r="AL2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AM2" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1879152</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="O3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P3"/>
       <c r="Q3"/>
       <c r="R3"/>
       <c r="S3"/>
       <c r="T3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="U3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="V3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="X3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Y3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Z3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA3"/>
       <c r="AB3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AC3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AD3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AE3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AF3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="AH3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AI3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
         <v>82</v>
@@ -1056,11 +1092,18 @@
         <v>90000000</v>
       </c>
       <c r="AL3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AM3" t="s">
-        <v>93</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1075,21 +1118,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
         <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -1103,82 +1146,106 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B3" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>90000000</v>
+        <v>1879152</v>
       </c>
       <c r="D3" t="n">
-        <v>47.5</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B4" t="n">
-        <v>110</v>
-      </c>
-      <c r="C4" t="n">
-        <v>121500000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>64.12</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>5618367</v>
+        <v>121500000</v>
       </c>
       <c r="D6" t="n">
-        <v>2.97</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B7"/>
+        <v>106</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
       <c r="C7" t="n">
-        <v>189477607.26</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8"/>
+        <v>107</v>
+      </c>
+      <c r="B8" t="n">
+        <v>18</v>
+      </c>
       <c r="C8" t="n">
-        <v>62359240.26</v>
+        <v>7344025</v>
       </c>
       <c r="D8" t="n">
-        <v>32.91</v>
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9" t="n">
+        <v>189477607.26</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10"/>
+      <c r="C10" t="n">
+        <v>60633582.26</v>
+      </c>
+      <c r="D10" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/SD_year1_awardees.xlsx
+++ b/SD_year1_awardees.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t xml:space="preserve">field</t>
   </si>
@@ -49,13 +49,13 @@
     <t xml:space="preserve">Where the names would be</t>
   </si>
   <si>
-    <t xml:space="preserve">open.sd.gov, as contracts are finalised: 8 of the 28 Rural Strong grants are there as of 2026-09-24 (R/03i); none of the 82 Technology and data grants.</t>
+    <t xml:space="preserve">open.sd.gov, as contracts are finalised (R/03i). As of 2026-10-02: 14 of the 28 Rural Strong grants, and 8 named awards whose round the register does not state (R/03i's UNPLACED pool) -- none of them is labelled a Technology and data grant.</t>
   </si>
   <si>
     <t xml:space="preserve">Do not add this to</t>
   </si>
   <si>
-    <t xml:space="preserve">data/reference/sd_rht_contracts.csv. Its ADMINISTRATIVE pool is in neither round; its RURAL STRONG pool (round_id RS) is INSIDE the $31.5M round here -- the same money named at a finer grain. Read named_elsewhere_grants / named_elsewhere_amount, and both headers, before combining anything.</t>
+    <t xml:space="preserve">data/reference/sd_rht_contracts.csv. Its ADMINISTRATIVE pool is in neither round; its RURAL STRONG pool (round_id RS) is INSIDE the $31.5M round here -- the same money named at a finer grain; its UNPLACED pool may be inside the $90M round and is never added to it. Read named_elsewhere_grants / named_elsewhere_amount, and both headers, before combining anything.</t>
   </si>
   <si>
     <t xml:space="preserve">Rebuild</t>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t xml:space="preserve">Technology and data grants (2026-08-19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  named awards on open.sd.gov whose round the register does NOT state (R/03i UNPLACED; MAY be inside the line above, never added)</t>
   </si>
   <si>
     <t xml:space="preserve">Announced rounds, total</t>
@@ -982,10 +985,10 @@
         <v>84</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AO2" t="n">
-        <v>1879152</v>
+        <v>15967960</v>
       </c>
       <c r="AP2" t="s">
         <v>85</v>
@@ -1149,13 +1152,13 @@
         <v>102</v>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>1879152</v>
+        <v>15967960</v>
       </c>
       <c r="D3" t="n">
-        <v>0.99</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="4">
@@ -1163,7 +1166,7 @@
         <v>103</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -1187,13 +1190,13 @@
         <v>105</v>
       </c>
       <c r="B6" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>121500000</v>
+        <v>3175112</v>
       </c>
       <c r="D6" t="n">
-        <v>64.12</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="7">
@@ -1201,13 +1204,13 @@
         <v>106</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>121500000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>64.12</v>
       </c>
     </row>
     <row r="8">
@@ -1215,25 +1218,27 @@
         <v>107</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>7344025</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>108</v>
       </c>
-      <c r="B9"/>
+      <c r="B9" t="n">
+        <v>19</v>
+      </c>
       <c r="C9" t="n">
-        <v>189477607.26</v>
+        <v>7693072</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="10">
@@ -1242,10 +1247,22 @@
       </c>
       <c r="B10"/>
       <c r="C10" t="n">
-        <v>60633582.26</v>
+        <v>189477607.26</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11"/>
+      <c r="C11" t="n">
+        <v>60284535.26</v>
+      </c>
+      <c r="D11" t="n">
+        <v>31.82</v>
       </c>
     </row>
   </sheetData>
